--- a/emergency_contact_form_templates/044_emergency_shelter_communication_form--emergency_contact_form_templates.xlsx
+++ b/emergency_contact_form_templates/044_emergency_shelter_communication_form--emergency_contact_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shelter Capacity</t>
+          <t>Emergency Shelter Capacity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shelter Population</t>
+          <t>Emergency Population</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>emergency_services</t>
+          <t>emergency_services_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency Services</t>
+          <t>Emergency Services 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Response Time</t>
+          <t>Emergency Response Time</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>emergency_status</t>
+          <t>emergency_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency Status</t>
+          <t>Emergency Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emergency_services_choices</t>
+          <t>emergency_services_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emergency_services_choices</t>
+          <t>emergency_services_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emergency_services_choices</t>
+          <t>emergency_services_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emergency_status_choices</t>
+          <t>emergency_status_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emergency_status_choices</t>
+          <t>emergency_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emergency_status_choices</t>
+          <t>emergency_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
